--- a/nyc_taxi_analysis/02_hypotheses/hypotheses.xlsx
+++ b/nyc_taxi_analysis/02_hypotheses/hypotheses.xlsx
@@ -439,7 +439,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -531,12 +531,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>total_amount</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fare_amount / trip_distance</t>
+          <t>total_amount / trip_distance</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Longer trips are expected to have higher fares, but the relationship may be influenced by fixed fees at airports.</t>
+          <t>Longer trips are expected to have higher total amounts, but the relationship may be influenced by flat fares for airport trips.</t>
         </is>
       </c>
     </row>
@@ -582,22 +582,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>trip_duration_minutes</t>
+          <t>passenger_count</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>fare_amount</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>fare_amount / trip_duration_minutes</t>
-        </is>
-      </c>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>monotonic</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -614,11 +610,11 @@
         <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Longer trip durations may lead to higher fares due to time-based charges.</t>
+          <t>More passengers might correlate with higher total amounts due to shared rides or negotiated fares.</t>
         </is>
       </c>
     </row>
@@ -638,19 +634,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>payment_type</t>
+          <t>pickup_hour</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>fare_amount</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>fare_amount</t>
-        </is>
-      </c>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>group_difference</t>
@@ -670,11 +662,11 @@
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Different payment types may be associated with different fare amounts due to varying tipping behaviors and fare adjustments.</t>
+          <t>Different times of day may have different fare structures due to rush hour surcharges.</t>
         </is>
       </c>
     </row>
@@ -694,19 +686,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>is_rush_hour</t>
+          <t>payment_type</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>fare_amount</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>fare_amount</t>
-        </is>
-      </c>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>group_difference</t>
@@ -714,7 +702,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -723,14 +711,14 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
         <v>0.1</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Rush hour trips may have higher fares due to increased demand and potential surcharges.</t>
+          <t>Different payment types might be associated with different total amounts due to tipping behavior and fare disputes.</t>
         </is>
       </c>
     </row>
@@ -750,22 +738,18 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VendorID</t>
+          <t>average_speed_mph</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>fare_amount</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>fare_amount</t>
-        </is>
-      </c>
+          <t>fare_per_mile</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>group_difference</t>
+          <t>nonlinear</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -779,14 +763,14 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Different vendors may have different fare structures or reporting practices.</t>
+          <t>The relationship between speed and fare per mile may be complex, as faster trips could be more efficient or incur higher surcharges.</t>
         </is>
       </c>
     </row>
@@ -806,43 +790,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pickup_hour</t>
+          <t>is_airport_pickup</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>fare_amount</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>fare_amount</t>
-        </is>
-      </c>
+          <t>total_per_mile</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nonlinear</t>
+          <t>group_difference</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Fares may vary by time of day due to demand fluctuations and surcharges.</t>
+          <t>Airport pickups include fixed fees that increase the total per mile compared to non-airport trips.</t>
         </is>
       </c>
     </row>
@@ -877,7 +857,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>linear; monotonic</t>
+          <t>nonlinear</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -891,14 +871,14 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="n">
         <v>0.2</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Investigating the relationship between trip distance and cost per mile could reveal how distance affects pricing efficiency, especially given the known fixed fees for airport pickups.</t>
+          <t>Exploring the nonlinear relationship between trip distance and cost per mile could reveal insights into how distance affects fare efficiency, especially given the known nonlinearities in previous tests.</t>
         </is>
       </c>
     </row>
@@ -918,7 +898,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>passenger_count</t>
+          <t>fare_per_mile</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -928,7 +908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>log1p(passenger_count)</t>
+          <t>log(fare_per_mile)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -938,7 +918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -947,14 +927,14 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
         <v>0.3</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Exploring how the number of passengers affects total fare could uncover nonlinear effects, especially given the high proportion of null and zero values.</t>
+          <t>Investigating the nonlinear relationship between fare per mile and total amount could help understand pricing dynamics, especially for trips with varying surcharges.</t>
         </is>
       </c>
     </row>
@@ -974,7 +954,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>payment_type</t>
+          <t>pickup_day_of_week</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1006,7 +986,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Different payment types may correlate with different fare amounts due to varying tipping behaviors and potential disputes.</t>
+          <t>Day of the week may influence taxi demand and pricing, potentially affecting total fare amounts due to varying traffic and demand patterns.</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1006,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>pickup_hour</t>
+          <t>is_rush_hour</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1042,7 +1022,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1051,14 +1031,14 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Time of day may influence fare amounts due to demand fluctuations and potential surcharges.</t>
+          <t>Rush hour conditions could lead to higher fares due to increased traffic and demand, impacting the total amount paid.</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1058,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>is_airport_pickup</t>
+          <t>VendorID</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>total_per_mile</t>
+          <t>total_amount</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1094,23 +1074,23 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K12" t="n">
         <v>0.1</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Airport pickups are known to have fixed fees, which could significantly affect the cost per mile, especially for short trips.</t>
+          <t>Different vendors may have varying pricing strategies or service quality, potentially affecting the total fare amount.</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1110,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VendorID</t>
+          <t>congestion_surcharge</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1141,12 +1121,12 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>group_difference</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1162,7 +1142,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Different vendors might have varying fare structures or service quality, potentially affecting total fare amounts.</t>
+          <t>Quantifying the impact of congestion surcharges on total fare could provide insights into how these fees contribute to overall trip costs.</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1162,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>trip_distance</t>
+          <t>trip_duration_minutes</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1192,7 +1172,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>total_per_mile</t>
+          <t>trip_duration_minutes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1211,14 +1191,14 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Testing the relationship between total amount per mile and trip distance could reveal how distance affects the cost efficiency of trips, especially considering airport fees.</t>
+          <t>Longer trip durations may be associated with higher total amounts due to increased time-based charges.</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1218,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>trip_duration_minutes</t>
+          <t>tip_fraction_of_fare</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1248,12 +1228,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>total_per_mile</t>
+          <t>tip_fraction_of_fare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>linear; monotonic</t>
+          <t>nonlinear</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1267,14 +1247,14 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
         <v>0.3</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Investigating total amount per mile against trip duration could highlight how time affects fare efficiency, especially during rush hours.</t>
+          <t>The proportion of the fare that is tipped could influence the total amount, especially for credit card payments.</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1274,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>payment_type</t>
+          <t>is_airport_pickup</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1304,7 +1284,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>fare_per_mile</t>
+          <t>is_airport_pickup</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1314,7 +1294,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1330,7 +1310,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Different payment types may influence fare per mile due to varying tipping behaviors and transaction fees.</t>
+          <t>Airport pickups likely incur additional fees, leading to higher total amounts compared to non-airport pickups.</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1330,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>is_airport_pickup</t>
+          <t>pickup_hour</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1360,7 +1340,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>total_per_mile</t>
+          <t>pickup_hour</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1370,23 +1350,23 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Airport pickups have fixed fees that could significantly affect the total cost per mile, revealing differences in fare structure.</t>
+          <t>Different pickup hours may reflect varying demand and surcharge conditions, potentially affecting total amounts.</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1386,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>pickup_day_of_week</t>
+          <t>payment_type</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1416,7 +1396,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>fare_per_mile</t>
+          <t>payment_type</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1438,11 +1418,11 @@
         <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Day of the week could influence fare per mile due to variations in demand and traffic patterns.</t>
+          <t>Different payment types might be associated with varying total amounts due to differences in tipping behavior and transaction fees.</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1442,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>passenger_count</t>
+          <t>RatecodeID</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1472,12 +1452,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>fare_per_mile</t>
+          <t>RatecodeID</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>nonlinear</t>
+          <t>group_difference</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1487,18 +1467,18 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.4</v>
       </c>
-      <c r="K19" t="n">
-        <v>0.3</v>
-      </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Passenger count might affect fare per mile in nonlinear ways due to shared ride dynamics and negotiated fares.</t>
+          <t>Different rate codes imply different fare structures, which could significantly impact the total amount.</t>
         </is>
       </c>
     </row>
